--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2021_magallanes.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:27</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>-0.16</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -587,7 +587,7 @@
         <v>-0.23</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -606,7 +606,7 @@
         <v>-0.2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -622,10 +622,10 @@
         <v>5</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -644,7 +644,7 @@
         <v>0.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -662,10 +662,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.28</v>
@@ -688,7 +688,7 @@
         <v>0.12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.07</v>
@@ -711,7 +711,7 @@
         <v>0.17</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.12</v>
@@ -732,7 +732,7 @@
         <v>0.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -751,7 +751,7 @@
         <v>0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -772,7 +772,7 @@
         <v>0.21</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.55</v>
@@ -795,7 +795,7 @@
         <v>0.19</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.49</v>
@@ -809,19 +809,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15">
@@ -832,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -855,19 +855,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -878,19 +878,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.56</v>
+        <v>-0.51</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.73</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="18">
@@ -908,7 +908,7 @@
         <v>-0.22</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2"/>
     </row>
@@ -929,7 +929,7 @@
         <v>-0.23</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.01</v>
@@ -952,10 +952,10 @@
         <v>-0.35</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="21">
@@ -966,19 +966,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.45</v>
+        <v>0.46</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.13</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.36</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="22">
@@ -989,19 +989,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.55</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="23">
@@ -1012,19 +1012,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.19</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
